--- a/examples/separator/cem.xlsx
+++ b/examples/separator/cem.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE37"/>
+  <dimension ref="A1:AF37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -457,16 +457,17 @@
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="42" customWidth="1" min="23" max="23"/>
-    <col width="20" customWidth="1" min="24" max="24"/>
-    <col width="42" customWidth="1" min="25" max="25"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="8" customWidth="1" min="23" max="23"/>
+    <col width="42" customWidth="1" min="24" max="24"/>
+    <col width="20" customWidth="1" min="25" max="25"/>
     <col width="42" customWidth="1" min="26" max="26"/>
     <col width="42" customWidth="1" min="27" max="27"/>
     <col width="42" customWidth="1" min="28" max="28"/>
     <col width="42" customWidth="1" min="29" max="29"/>
     <col width="42" customWidth="1" min="30" max="30"/>
     <col width="42" customWidth="1" min="31" max="31"/>
+    <col width="42" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -579,7 +580,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -591,7 +592,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -675,252 +676,252 @@
       </c>
     </row>
     <row r="21">
-      <c r="X21" s="3" t="inlineStr">
+      <c r="Y21" s="3" t="inlineStr">
         <is>
           <t>effect_no</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
+      <c r="Z21" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Z21" s="3" t="inlineStr">
+      <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="3" t="inlineStr">
+      <c r="AB21" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB21" s="3" t="inlineStr">
+      <c r="AC21" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AC21" s="3" t="inlineStr">
+      <c r="AD21" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AD21" s="3" t="inlineStr">
+      <c r="AE21" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AE21" s="3" t="inlineStr">
+      <c r="AF21" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="X22" s="3" t="inlineStr">
+      <c r="Y22" s="3" t="inlineStr">
         <is>
           <t>effect_tag</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
+      <c r="Z22" s="3" t="inlineStr">
         <is>
           <t>ESDV101</t>
         </is>
       </c>
-      <c r="Z22" s="3" t="inlineStr">
+      <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>BDV101</t>
         </is>
       </c>
-      <c r="AA22" s="3" t="inlineStr">
+      <c r="AB22" s="3" t="inlineStr">
         <is>
           <t>ESDV102</t>
         </is>
       </c>
-      <c r="AB22" s="3" t="inlineStr">
+      <c r="AC22" s="3" t="inlineStr">
         <is>
           <t>P101A</t>
         </is>
       </c>
-      <c r="AC22" s="3" t="inlineStr">
+      <c r="AD22" s="3" t="inlineStr">
         <is>
           <t>P101B</t>
         </is>
       </c>
-      <c r="AD22" s="3" t="inlineStr">
+      <c r="AE22" s="3" t="inlineStr">
         <is>
           <t>H101</t>
         </is>
       </c>
-      <c r="AE22" s="3" t="inlineStr">
+      <c r="AF22" s="3" t="inlineStr">
         <is>
           <t>UA110</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="X23" s="3" t="inlineStr">
+      <c r="Y23" s="3" t="inlineStr">
         <is>
           <t>effect_description</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="inlineStr">
+      <c r="Z23" s="3" t="inlineStr">
         <is>
           <t>Клапан-отсекатель на входе V-101</t>
         </is>
       </c>
-      <c r="Z23" s="4" t="inlineStr">
+      <c r="AA23" s="4" t="inlineStr">
         <is>
           <t>Клапан аварийного сброса давления на факел</t>
         </is>
       </c>
-      <c r="AA23" s="3" t="inlineStr">
+      <c r="AB23" s="3" t="inlineStr">
         <is>
           <t>Клапан-отсекатель на линии нефти</t>
         </is>
       </c>
-      <c r="AB23" s="3" t="inlineStr">
+      <c r="AC23" s="3" t="inlineStr">
         <is>
           <t>Насос откачки нефти P-101A</t>
         </is>
       </c>
-      <c r="AC23" s="3" t="inlineStr">
+      <c r="AD23" s="3" t="inlineStr">
         <is>
           <t>Насос откачки нефти P-101B</t>
         </is>
       </c>
-      <c r="AD23" s="4" t="inlineStr">
+      <c r="AE23" s="4" t="inlineStr">
         <is>
           <t>Погружной электронагреватель H-101 в V-101</t>
         </is>
       </c>
-      <c r="AE23" s="3" t="inlineStr">
+      <c r="AF23" s="3" t="inlineStr">
         <is>
           <t>Общая сигнализация «Срабатывание ПАЗ»</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="X24" s="3" t="inlineStr">
+      <c r="Y24" s="3" t="inlineStr">
         <is>
           <t>actuator</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
+      <c r="Z24" s="3" t="inlineStr">
         <is>
           <t>Соленоид SOV-101, 24 В DC</t>
         </is>
       </c>
-      <c r="Z24" s="3" t="inlineStr">
+      <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Соленоид SOV-102, 24 В DC</t>
         </is>
       </c>
-      <c r="AA24" s="3" t="inlineStr">
+      <c r="AB24" s="3" t="inlineStr">
         <is>
           <t>Соленоид SOV-103, 24 В DC</t>
         </is>
       </c>
-      <c r="AB24" s="4" t="inlineStr">
+      <c r="AC24" s="4" t="inlineStr">
         <is>
           <t>Реле разрешения работы в схеме управления P-101A</t>
         </is>
       </c>
-      <c r="AC24" s="4" t="inlineStr">
+      <c r="AD24" s="4" t="inlineStr">
         <is>
           <t>Реле разрешения работы в схеме управления P-101B</t>
         </is>
       </c>
-      <c r="AD24" s="4" t="inlineStr">
+      <c r="AE24" s="4" t="inlineStr">
         <is>
           <t>Реле разрешения работы в схеме питания H-101</t>
         </is>
       </c>
-      <c r="AE24" s="3" t="inlineStr">
+      <c r="AF24" s="3" t="inlineStr">
         <is>
           <t>Реле сирены и табло в операторной</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="X25" s="3" t="inlineStr">
+      <c r="Y25" s="3" t="inlineStr">
         <is>
           <t>safe_state</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
+      <c r="Z25" s="3" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="Z25" s="3" t="inlineStr">
+      <c r="AA25" s="3" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="AA25" s="3" t="inlineStr">
+      <c r="AB25" s="3" t="inlineStr">
         <is>
           <t>closed</t>
         </is>
       </c>
-      <c r="AB25" s="3" t="inlineStr">
+      <c r="AC25" s="3" t="inlineStr">
         <is>
           <t>stopped</t>
         </is>
       </c>
-      <c r="AC25" s="3" t="inlineStr">
+      <c r="AD25" s="3" t="inlineStr">
         <is>
           <t>stopped</t>
         </is>
       </c>
-      <c r="AD25" s="3" t="inlineStr">
+      <c r="AE25" s="3" t="inlineStr">
         <is>
           <t>off</t>
         </is>
       </c>
-      <c r="AE25" s="3" t="inlineStr">
+      <c r="AF25" s="3" t="inlineStr">
         <is>
           <t>alarm</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="X26" s="3" t="inlineStr">
+      <c r="Y26" s="3" t="inlineStr">
         <is>
           <t>effect_notes</t>
         </is>
       </c>
-      <c r="Y26" s="4" t="inlineStr">
+      <c r="Z26" s="4" t="inlineStr">
         <is>
           <t>Закрывается пружиной при обесточивании соленоида</t>
         </is>
       </c>
-      <c r="Z26" s="4" t="inlineStr">
+      <c r="AA26" s="4" t="inlineStr">
         <is>
           <t>Открывается пружиной при обесточивании соленоида</t>
         </is>
       </c>
-      <c r="AA26" s="4" t="inlineStr">
+      <c r="AB26" s="4" t="inlineStr">
         <is>
           <t>Закрывается пружиной при обесточивании соленоида</t>
         </is>
       </c>
-      <c r="AB26" s="4" t="inlineStr">
+      <c r="AC26" s="4" t="inlineStr">
         <is>
           <t>Повторный пуск — только оператором после сброса ПАЗ</t>
         </is>
       </c>
-      <c r="AC26" s="4" t="inlineStr">
+      <c r="AD26" s="4" t="inlineStr">
         <is>
           <t>Повторный пуск — только оператором после сброса ПАЗ</t>
         </is>
       </c>
-      <c r="AD26" s="4" t="inlineStr">
+      <c r="AE26" s="4" t="inlineStr">
         <is>
           <t>Повторное включение — только оператором после сброса ПАЗ</t>
         </is>
       </c>
-      <c r="AE26" s="4" t="inlineStr">
+      <c r="AF26" s="4" t="inlineStr">
         <is>
           <t>Сирена включается размыкающим контактом обесточенного реле</t>
         </is>
@@ -1034,15 +1035,20 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
+          <t>override_clear</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
           <t>enable</t>
         </is>
       </c>
-      <c r="W27" s="2" t="inlineStr">
+      <c r="X27" s="2" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr">
+      <c r="Y27" s="2" t="inlineStr">
         <is>
           <t>&gt;&gt;</t>
         </is>
@@ -1149,27 +1155,27 @@
           <t>no</t>
         </is>
       </c>
-      <c r="V28" s="3" t="inlineStr">
+      <c r="W28" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="W28" s="4" t="inlineStr">
+      <c r="X28" s="4" t="inlineStr">
         <is>
           <t>Уставка ниже давления настройки предохранительного клапана</t>
         </is>
       </c>
-      <c r="Y28" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AD28" s="3" t="inlineStr">
+      <c r="Z28" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1283,20 +1289,20 @@
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
+          <t>30s</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="W29" s="4" t="inlineStr">
-        <is>
-          <t>Пусковой обход: при пуске сепаратор набирает давление</t>
-        </is>
-      </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AA29" s="3" t="inlineStr">
+      <c r="X29" s="4" t="inlineStr">
+        <is>
+          <t>Пусковой обход: при пуске сепаратор набирает давление. Обход снимается сам после 30 с устойчивой нормы (6 задержек причины): выдержка отсеивает колебания давления у уставки при наборе, а защита от повторного падения давления возвращается задолго до конца срока 15 мин</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1317,6 +1323,11 @@
         </is>
       </c>
       <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1423,27 +1434,27 @@
           <t>no</t>
         </is>
       </c>
-      <c r="V30" s="3" t="inlineStr">
+      <c r="W30" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="W30" s="3" t="inlineStr">
+      <c r="X30" s="3" t="inlineStr">
         <is>
           <t>Унос жидкости в газовую линию</t>
         </is>
       </c>
-      <c r="Y30" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AD30" s="3" t="inlineStr">
+      <c r="Z30" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
       <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1557,17 +1568,17 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="W31" s="4" t="inlineStr">
-        <is>
-          <t>Прорыв газа в линию нефти и оголение нагревателя, пусковой обход на время заполнения</t>
-        </is>
-      </c>
-      <c r="AA31" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
+      <c r="X31" s="4" t="inlineStr">
+        <is>
+          <t>Прорыв газа в линию нефти и оголение нагревателя, пусковой обход на время заполнения. Обход снимается сам после 1 мин устойчивой нормы: уровень при заполнении колеблется от притока и пены, нужна более длинная выдержка, чем у давления</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
@@ -1586,6 +1597,11 @@
         </is>
       </c>
       <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1692,22 +1708,22 @@
           <t>no</t>
         </is>
       </c>
-      <c r="V32" s="3" t="inlineStr">
+      <c r="W32" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="W32" s="3" t="inlineStr">
+      <c r="X32" s="3" t="inlineStr">
         <is>
           <t>Перегрев эмульсии погружным нагревателем</t>
         </is>
       </c>
-      <c r="AD32" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1814,22 +1830,17 @@
           <t>no</t>
         </is>
       </c>
-      <c r="V33" s="3" t="inlineStr">
+      <c r="W33" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="W33" s="4" t="inlineStr">
+      <c r="X33" s="4" t="inlineStr">
         <is>
           <t>Предупредительная сигнализация 20 % НКПР — в системе обнаружения газа, вне ПАЗ, уставки сверить с нормами</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AA33" s="3" t="inlineStr">
+      <c r="Z33" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1850,6 +1861,11 @@
         </is>
       </c>
       <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -1916,21 +1932,16 @@
           <t>no</t>
         </is>
       </c>
-      <c r="V34" s="3" t="inlineStr">
+      <c r="W34" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="W34" s="4" t="inlineStr">
+      <c r="X34" s="4" t="inlineStr">
         <is>
           <t>Извещатели пламени, нормально замкнутый контакт «Пожар», контроль линии</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -1957,6 +1968,11 @@
         </is>
       </c>
       <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2023,21 +2039,16 @@
           <t>no</t>
         </is>
       </c>
-      <c r="V35" s="3" t="inlineStr">
+      <c r="W35" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="W35" s="4" t="inlineStr">
+      <c r="X35" s="4" t="inlineStr">
         <is>
           <t>HS106A — операторная, HS106B — по месту, байпас запрещён</t>
         </is>
       </c>
-      <c r="Y35" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -2064,6 +2075,11 @@
         </is>
       </c>
       <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2137,20 +2153,20 @@
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
+          <t>30s</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="W36" s="4" t="inlineStr">
-        <is>
-          <t>Реле давления, 2oo2 — защита от ложного останова, пусковой обход на время пуска компрессорной</t>
-        </is>
-      </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="AA36" s="3" t="inlineStr">
+      <c r="X36" s="4" t="inlineStr">
+        <is>
+          <t>Реле давления, 2oo2 — защита от ложного останова, пусковой обход на время пуска компрессорной. Обход снимается сам после 30 с устойчивой нормы: реле может дребезжать у порога, пока заполняется ресивер</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2171,6 +2187,11 @@
         </is>
       </c>
       <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -2237,21 +2258,16 @@
           <t>no</t>
         </is>
       </c>
-      <c r="V37" s="3" t="inlineStr">
+      <c r="W37" s="3" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="W37" s="4" t="inlineStr">
+      <c r="X37" s="4" t="inlineStr">
         <is>
           <t>Реле контроля напряжения, байпас запрещён</t>
         </is>
       </c>
-      <c r="AB37" s="3" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
           <t>X</t>
@@ -2263,6 +2279,11 @@
         </is>
       </c>
       <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
         <is>
           <t>X</t>
         </is>

--- a/examples/separator/cem.xlsx
+++ b/examples/separator/cem.xlsx
@@ -604,7 +604,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>&lt;ИМЯ ФАМИЛИЯ&gt;</t>
+          <t>kr0nsch</t>
         </is>
       </c>
     </row>
